--- a/report-004-manual-004.xlsx
+++ b/report-004-manual-004.xlsx
@@ -566,7 +566,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>{"baseline_commit": "f7bcbd460cdbb6d7f0804fee4e36e0dbf22c7eca", "fix_commit": "852e89e89f115333a3503b5fbd714e72d48711c7", "fix_passed": true, "red_failed": true, "test_commit": "1acecd3211e3e5634e52aad14dc13f3c824d8d5c"}</t>
+          <t>{"pre_fix": {"commit": "1acecd3211e3e5634e52aad14dc13f3c824d8d5c", "result": "red", "trajectory_url": "未生成"}}</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
